--- a/Sample_run/1/student/dungdvhe181404/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/dungdvhe181404/TC6/GradeDetail.xlsx
@@ -209,16 +209,16 @@
     <x:t>Client closing connection</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
     <x:t>S111</x:t>
   </x:si>
   <x:si>
     <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1107,7 +1107,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1166,7 +1166,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1219,7 +1219,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1275,7 +1275,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1334,7 +1334,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1390,7 +1390,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>58</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1546,22 +1546,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>54242</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>41704</x:v>
+      </x:c>
+      <x:c r="R10" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1611,7 +1611,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54242</x:v>
+        <x:v>41704</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1652,28 +1652,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>54242</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="4" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1723,7 +1723,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1782,7 +1782,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1867,7 +1867,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>46</x:v>
@@ -1888,10 +1888,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1950,7 +1950,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -1979,7 +1979,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>47</x:v>
@@ -2006,7 +2006,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
         <x:v>58</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2118,7 +2118,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2174,7 +2174,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2227,7 +2227,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>48020</x:v>
+        <x:v>51060</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2268,7 +2268,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2289,7 +2289,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="R23" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
